--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_LinhKienGiaCongVNSH03_160626.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_LinhKienGiaCongVNSH03_160626.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Xuất kho\Tháng 06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC4CC8B-5BB2-4F45-A1A5-53F37F1D36A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1885CDDA-5DE8-4765-982F-1D144CC48BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1038,71 +1038,71 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1539,61 +1539,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="45" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="47"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="46"/>
     </row>
     <row r="2" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="39"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="48" t="s">
+      <c r="A2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="49"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
     </row>
     <row r="3" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="39"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="48" t="s">
+      <c r="A3" s="38"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="49"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
     </row>
     <row r="4" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="42"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="50" t="s">
+      <c r="A4" s="41"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="51"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
     </row>
     <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="35"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="34"/>
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
@@ -2451,7 +2451,7 @@
         <v>1000</v>
       </c>
       <c r="E56" s="21"/>
-      <c r="F56" s="30" t="s">
+      <c r="F56" s="51" t="s">
         <v>205</v>
       </c>
       <c r="G56" s="21" t="s">
@@ -2472,7 +2472,7 @@
         <v>500</v>
       </c>
       <c r="E57" s="21"/>
-      <c r="F57" s="30"/>
+      <c r="F57" s="51"/>
       <c r="G57" s="21"/>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2489,7 +2489,7 @@
         <v>500</v>
       </c>
       <c r="E58" s="21"/>
-      <c r="F58" s="30"/>
+      <c r="F58" s="51"/>
       <c r="G58" s="21"/>
     </row>
     <row r="59" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2506,7 +2506,7 @@
         <v>1000</v>
       </c>
       <c r="E59" s="21"/>
-      <c r="F59" s="30"/>
+      <c r="F59" s="51"/>
       <c r="G59" s="21"/>
     </row>
     <row r="60" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2523,7 +2523,7 @@
         <v>5000</v>
       </c>
       <c r="E60" s="21"/>
-      <c r="F60" s="30"/>
+      <c r="F60" s="51"/>
       <c r="G60" s="21"/>
     </row>
     <row r="61" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2540,7 +2540,7 @@
         <v>3000</v>
       </c>
       <c r="E61" s="21"/>
-      <c r="F61" s="30"/>
+      <c r="F61" s="51"/>
       <c r="G61" s="21"/>
     </row>
     <row r="62" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2557,7 +2557,7 @@
         <v>6500</v>
       </c>
       <c r="E62" s="21"/>
-      <c r="F62" s="30"/>
+      <c r="F62" s="51"/>
       <c r="G62" s="21"/>
     </row>
     <row r="63" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2574,7 +2574,7 @@
         <v>1000</v>
       </c>
       <c r="E63" s="21"/>
-      <c r="F63" s="30"/>
+      <c r="F63" s="51"/>
       <c r="G63" s="21"/>
     </row>
     <row r="64" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2591,7 +2591,7 @@
         <v>500</v>
       </c>
       <c r="E64" s="21"/>
-      <c r="F64" s="30"/>
+      <c r="F64" s="51"/>
       <c r="G64" s="21"/>
     </row>
     <row r="65" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2608,7 +2608,7 @@
         <v>1000</v>
       </c>
       <c r="E65" s="21"/>
-      <c r="F65" s="30"/>
+      <c r="F65" s="51"/>
       <c r="G65" s="21"/>
     </row>
     <row r="66" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2625,7 +2625,7 @@
         <v>500</v>
       </c>
       <c r="E66" s="21"/>
-      <c r="F66" s="30"/>
+      <c r="F66" s="51"/>
       <c r="G66" s="21"/>
     </row>
     <row r="67" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2642,7 +2642,7 @@
         <v>500</v>
       </c>
       <c r="E67" s="21"/>
-      <c r="F67" s="30"/>
+      <c r="F67" s="51"/>
       <c r="G67" s="21"/>
     </row>
     <row r="68" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2659,7 +2659,7 @@
         <v>2000</v>
       </c>
       <c r="E68" s="21"/>
-      <c r="F68" s="30"/>
+      <c r="F68" s="51"/>
       <c r="G68" s="21"/>
     </row>
     <row r="69" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2676,7 +2676,7 @@
         <v>1500</v>
       </c>
       <c r="E69" s="21"/>
-      <c r="F69" s="30"/>
+      <c r="F69" s="51"/>
       <c r="G69" s="21"/>
     </row>
     <row r="70" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2693,7 +2693,7 @@
         <v>1000</v>
       </c>
       <c r="E70" s="21"/>
-      <c r="F70" s="30"/>
+      <c r="F70" s="51"/>
       <c r="G70" s="21"/>
     </row>
     <row r="71" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2710,7 +2710,7 @@
         <v>500</v>
       </c>
       <c r="E71" s="21"/>
-      <c r="F71" s="30"/>
+      <c r="F71" s="51"/>
       <c r="G71" s="21"/>
     </row>
     <row r="72" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2727,7 +2727,7 @@
         <v>500</v>
       </c>
       <c r="E72" s="21"/>
-      <c r="F72" s="30"/>
+      <c r="F72" s="51"/>
       <c r="G72" s="21"/>
     </row>
     <row r="73" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2744,7 +2744,7 @@
         <v>500</v>
       </c>
       <c r="E73" s="21"/>
-      <c r="F73" s="30"/>
+      <c r="F73" s="51"/>
       <c r="G73" s="21"/>
     </row>
     <row r="74" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2761,7 +2761,7 @@
         <v>500</v>
       </c>
       <c r="E74" s="21"/>
-      <c r="F74" s="30"/>
+      <c r="F74" s="51"/>
       <c r="G74" s="21"/>
     </row>
     <row r="75" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2778,7 +2778,7 @@
         <v>500</v>
       </c>
       <c r="E75" s="21"/>
-      <c r="F75" s="30"/>
+      <c r="F75" s="51"/>
       <c r="G75" s="21"/>
     </row>
     <row r="76" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2795,7 +2795,7 @@
         <v>500</v>
       </c>
       <c r="E76" s="21"/>
-      <c r="F76" s="30"/>
+      <c r="F76" s="51"/>
       <c r="G76" s="21"/>
     </row>
     <row r="77" spans="1:7" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
@@ -2812,7 +2812,7 @@
         <v>500</v>
       </c>
       <c r="E77" s="21"/>
-      <c r="F77" s="30"/>
+      <c r="F77" s="51"/>
       <c r="G77" s="21"/>
     </row>
     <row r="78" spans="1:7" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
@@ -2829,7 +2829,7 @@
         <v>500</v>
       </c>
       <c r="E78" s="21"/>
-      <c r="F78" s="30"/>
+      <c r="F78" s="51"/>
       <c r="G78" s="21"/>
     </row>
     <row r="79" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2846,7 +2846,7 @@
         <v>1000</v>
       </c>
       <c r="E79" s="21"/>
-      <c r="F79" s="30"/>
+      <c r="F79" s="51"/>
       <c r="G79" s="21"/>
     </row>
     <row r="80" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2863,7 +2863,7 @@
         <v>500</v>
       </c>
       <c r="E80" s="21"/>
-      <c r="F80" s="30"/>
+      <c r="F80" s="51"/>
       <c r="G80" s="21"/>
     </row>
     <row r="81" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2880,7 +2880,7 @@
         <v>500</v>
       </c>
       <c r="E81" s="21"/>
-      <c r="F81" s="30"/>
+      <c r="F81" s="51"/>
       <c r="G81" s="21"/>
     </row>
     <row r="82" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2897,7 +2897,7 @@
         <v>1500</v>
       </c>
       <c r="E82" s="21"/>
-      <c r="F82" s="30"/>
+      <c r="F82" s="51"/>
       <c r="G82" s="21"/>
     </row>
     <row r="83" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2914,7 +2914,7 @@
         <v>1500</v>
       </c>
       <c r="E83" s="21"/>
-      <c r="F83" s="30"/>
+      <c r="F83" s="51"/>
       <c r="G83" s="21"/>
     </row>
     <row r="84" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2931,7 +2931,7 @@
         <v>500</v>
       </c>
       <c r="E84" s="21"/>
-      <c r="F84" s="30"/>
+      <c r="F84" s="51"/>
       <c r="G84" s="21"/>
     </row>
     <row r="85" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2948,7 +2948,7 @@
         <v>3500</v>
       </c>
       <c r="E85" s="21"/>
-      <c r="F85" s="30"/>
+      <c r="F85" s="51"/>
       <c r="G85" s="21"/>
     </row>
     <row r="86" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2965,7 +2965,7 @@
         <v>500</v>
       </c>
       <c r="E86" s="21"/>
-      <c r="F86" s="30"/>
+      <c r="F86" s="51"/>
       <c r="G86" s="21"/>
     </row>
     <row r="87" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2982,7 +2982,7 @@
         <v>3500</v>
       </c>
       <c r="E87" s="21"/>
-      <c r="F87" s="30"/>
+      <c r="F87" s="51"/>
       <c r="G87" s="21"/>
     </row>
     <row r="88" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2999,7 +2999,7 @@
         <v>500</v>
       </c>
       <c r="E88" s="21"/>
-      <c r="F88" s="30"/>
+      <c r="F88" s="51"/>
       <c r="G88" s="21"/>
     </row>
     <row r="89" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3016,7 +3016,7 @@
         <v>500</v>
       </c>
       <c r="E89" s="21"/>
-      <c r="F89" s="30"/>
+      <c r="F89" s="51"/>
       <c r="G89" s="21"/>
     </row>
     <row r="90" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3033,7 +3033,7 @@
         <v>5000</v>
       </c>
       <c r="E90" s="21"/>
-      <c r="F90" s="30"/>
+      <c r="F90" s="51"/>
       <c r="G90" s="21"/>
     </row>
     <row r="91" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3050,7 +3050,7 @@
         <v>500</v>
       </c>
       <c r="E91" s="21"/>
-      <c r="F91" s="30"/>
+      <c r="F91" s="51"/>
       <c r="G91" s="21"/>
     </row>
     <row r="92" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3067,7 +3067,7 @@
         <v>500</v>
       </c>
       <c r="E92" s="21"/>
-      <c r="F92" s="30"/>
+      <c r="F92" s="51"/>
       <c r="G92" s="21"/>
     </row>
     <row r="93" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3084,7 +3084,7 @@
         <v>21980</v>
       </c>
       <c r="E93" s="21"/>
-      <c r="F93" s="30"/>
+      <c r="F93" s="51"/>
       <c r="G93" s="21"/>
     </row>
     <row r="94" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3101,7 +3101,7 @@
         <v>17000</v>
       </c>
       <c r="E94" s="21"/>
-      <c r="F94" s="30"/>
+      <c r="F94" s="51"/>
       <c r="G94" s="21"/>
     </row>
     <row r="95" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3118,7 +3118,7 @@
         <v>500</v>
       </c>
       <c r="E95" s="21"/>
-      <c r="F95" s="30"/>
+      <c r="F95" s="51"/>
       <c r="G95" s="21"/>
     </row>
     <row r="96" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3135,7 +3135,7 @@
         <v>500</v>
       </c>
       <c r="E96" s="21"/>
-      <c r="F96" s="30"/>
+      <c r="F96" s="51"/>
       <c r="G96" s="21"/>
     </row>
     <row r="97" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3152,7 +3152,7 @@
         <v>1000</v>
       </c>
       <c r="E97" s="21"/>
-      <c r="F97" s="30"/>
+      <c r="F97" s="51"/>
       <c r="G97" s="21"/>
     </row>
     <row r="98" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3169,7 +3169,7 @@
         <v>500</v>
       </c>
       <c r="E98" s="21"/>
-      <c r="F98" s="30"/>
+      <c r="F98" s="51"/>
       <c r="G98" s="21"/>
     </row>
     <row r="99" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3186,7 +3186,7 @@
         <v>500</v>
       </c>
       <c r="E99" s="21"/>
-      <c r="F99" s="30"/>
+      <c r="F99" s="51"/>
       <c r="G99" s="21"/>
     </row>
     <row r="100" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3203,7 +3203,7 @@
         <v>500</v>
       </c>
       <c r="E100" s="21"/>
-      <c r="F100" s="30"/>
+      <c r="F100" s="51"/>
       <c r="G100" s="21"/>
     </row>
     <row r="101" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3220,7 +3220,7 @@
         <v>2500</v>
       </c>
       <c r="E101" s="21"/>
-      <c r="F101" s="30"/>
+      <c r="F101" s="51"/>
       <c r="G101" s="21"/>
     </row>
     <row r="102" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3237,7 +3237,7 @@
         <v>9500</v>
       </c>
       <c r="E102" s="21"/>
-      <c r="F102" s="30"/>
+      <c r="F102" s="51"/>
       <c r="G102" s="21"/>
     </row>
     <row r="103" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3254,7 +3254,7 @@
         <v>500</v>
       </c>
       <c r="E103" s="21"/>
-      <c r="F103" s="30"/>
+      <c r="F103" s="51"/>
       <c r="G103" s="21"/>
     </row>
     <row r="104" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3271,7 +3271,7 @@
         <v>500</v>
       </c>
       <c r="E104" s="21"/>
-      <c r="F104" s="30"/>
+      <c r="F104" s="51"/>
       <c r="G104" s="21"/>
     </row>
     <row r="105" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3288,7 +3288,7 @@
         <v>500</v>
       </c>
       <c r="E105" s="21"/>
-      <c r="F105" s="30"/>
+      <c r="F105" s="51"/>
       <c r="G105" s="21"/>
     </row>
     <row r="106" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3305,7 +3305,7 @@
         <v>500</v>
       </c>
       <c r="E106" s="21"/>
-      <c r="F106" s="30"/>
+      <c r="F106" s="51"/>
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3322,7 +3322,7 @@
         <v>7500</v>
       </c>
       <c r="E107" s="21"/>
-      <c r="F107" s="30"/>
+      <c r="F107" s="51"/>
       <c r="G107" s="21"/>
     </row>
     <row r="108" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3339,7 +3339,7 @@
         <v>1000</v>
       </c>
       <c r="E108" s="21"/>
-      <c r="F108" s="30" t="s">
+      <c r="F108" s="51" t="s">
         <v>205</v>
       </c>
       <c r="G108" s="21"/>
@@ -3358,7 +3358,7 @@
         <v>14000</v>
       </c>
       <c r="E109" s="21"/>
-      <c r="F109" s="30"/>
+      <c r="F109" s="51"/>
       <c r="G109" s="21"/>
     </row>
     <row r="110" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3375,7 +3375,7 @@
         <v>500</v>
       </c>
       <c r="E110" s="21"/>
-      <c r="F110" s="30"/>
+      <c r="F110" s="51"/>
       <c r="G110" s="21"/>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3392,7 +3392,7 @@
         <v>1000</v>
       </c>
       <c r="E111" s="21"/>
-      <c r="F111" s="30"/>
+      <c r="F111" s="51"/>
       <c r="G111" s="21"/>
     </row>
     <row r="112" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3409,7 +3409,7 @@
         <v>11500</v>
       </c>
       <c r="E112" s="21"/>
-      <c r="F112" s="30"/>
+      <c r="F112" s="51"/>
       <c r="G112" s="21"/>
     </row>
     <row r="113" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3426,7 +3426,7 @@
         <v>500</v>
       </c>
       <c r="E113" s="21"/>
-      <c r="F113" s="30"/>
+      <c r="F113" s="51"/>
       <c r="G113" s="21"/>
     </row>
     <row r="114" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3443,7 +3443,7 @@
         <v>500</v>
       </c>
       <c r="E114" s="21"/>
-      <c r="F114" s="30"/>
+      <c r="F114" s="51"/>
       <c r="G114" s="21"/>
     </row>
     <row r="115" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3460,7 +3460,7 @@
         <v>4500</v>
       </c>
       <c r="E115" s="21"/>
-      <c r="F115" s="30"/>
+      <c r="F115" s="51"/>
       <c r="G115" s="21"/>
     </row>
     <row r="116" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3477,7 +3477,7 @@
         <v>2000</v>
       </c>
       <c r="E116" s="21"/>
-      <c r="F116" s="30"/>
+      <c r="F116" s="51"/>
       <c r="G116" s="21"/>
     </row>
     <row r="117" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3494,7 +3494,7 @@
         <v>500</v>
       </c>
       <c r="E117" s="21"/>
-      <c r="F117" s="30"/>
+      <c r="F117" s="51"/>
       <c r="G117" s="21"/>
     </row>
     <row r="118" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3511,7 +3511,7 @@
         <v>10000</v>
       </c>
       <c r="E118" s="21"/>
-      <c r="F118" s="30"/>
+      <c r="F118" s="51"/>
       <c r="G118" s="21"/>
     </row>
     <row r="119" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3528,7 +3528,7 @@
         <v>500</v>
       </c>
       <c r="E119" s="21"/>
-      <c r="F119" s="30"/>
+      <c r="F119" s="51"/>
       <c r="G119" s="21"/>
     </row>
     <row r="120" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3545,7 +3545,7 @@
         <v>500</v>
       </c>
       <c r="E120" s="21"/>
-      <c r="F120" s="30"/>
+      <c r="F120" s="51"/>
       <c r="G120" s="21"/>
     </row>
     <row r="121" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3562,7 +3562,7 @@
         <v>500</v>
       </c>
       <c r="E121" s="21"/>
-      <c r="F121" s="30"/>
+      <c r="F121" s="51"/>
       <c r="G121" s="21"/>
     </row>
     <row r="122" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3579,7 +3579,7 @@
         <v>500</v>
       </c>
       <c r="E122" s="21"/>
-      <c r="F122" s="30"/>
+      <c r="F122" s="51"/>
       <c r="G122" s="21"/>
     </row>
     <row r="123" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3596,7 +3596,7 @@
         <v>500</v>
       </c>
       <c r="E123" s="21"/>
-      <c r="F123" s="30"/>
+      <c r="F123" s="51"/>
       <c r="G123" s="21"/>
     </row>
     <row r="124" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3613,7 +3613,7 @@
         <v>500</v>
       </c>
       <c r="E124" s="21"/>
-      <c r="F124" s="30"/>
+      <c r="F124" s="51"/>
       <c r="G124" s="21"/>
     </row>
     <row r="125" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3630,7 +3630,7 @@
         <v>500</v>
       </c>
       <c r="E125" s="21"/>
-      <c r="F125" s="30"/>
+      <c r="F125" s="51"/>
       <c r="G125" s="21"/>
     </row>
     <row r="126" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3647,7 +3647,7 @@
         <v>500</v>
       </c>
       <c r="E126" s="21"/>
-      <c r="F126" s="30"/>
+      <c r="F126" s="51"/>
       <c r="G126" s="21"/>
     </row>
     <row r="127" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3664,7 +3664,7 @@
         <v>500</v>
       </c>
       <c r="E127" s="21"/>
-      <c r="F127" s="30"/>
+      <c r="F127" s="51"/>
       <c r="G127" s="21"/>
     </row>
     <row r="128" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3681,7 +3681,7 @@
         <v>1340</v>
       </c>
       <c r="E128" s="21"/>
-      <c r="F128" s="30"/>
+      <c r="F128" s="51"/>
       <c r="G128" s="21"/>
     </row>
     <row r="129" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3698,7 +3698,7 @@
         <v>500</v>
       </c>
       <c r="E129" s="21"/>
-      <c r="F129" s="30"/>
+      <c r="F129" s="51"/>
       <c r="G129" s="21"/>
     </row>
     <row r="130" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3715,7 +3715,7 @@
         <v>500</v>
       </c>
       <c r="E130" s="21"/>
-      <c r="F130" s="30"/>
+      <c r="F130" s="51"/>
       <c r="G130" s="21"/>
     </row>
     <row r="131" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3732,7 +3732,7 @@
         <v>12000</v>
       </c>
       <c r="E131" s="21"/>
-      <c r="F131" s="30"/>
+      <c r="F131" s="51"/>
       <c r="G131" s="21"/>
     </row>
     <row r="132" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3749,7 +3749,7 @@
         <v>500</v>
       </c>
       <c r="E132" s="21"/>
-      <c r="F132" s="30"/>
+      <c r="F132" s="51"/>
       <c r="G132" s="21"/>
     </row>
     <row r="133" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3766,7 +3766,7 @@
         <v>500</v>
       </c>
       <c r="E133" s="21"/>
-      <c r="F133" s="30"/>
+      <c r="F133" s="51"/>
       <c r="G133" s="21"/>
     </row>
     <row r="134" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3783,7 +3783,7 @@
         <v>1490</v>
       </c>
       <c r="E134" s="21"/>
-      <c r="F134" s="30"/>
+      <c r="F134" s="51"/>
       <c r="G134" s="21"/>
     </row>
     <row r="135" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3800,7 +3800,7 @@
         <v>500</v>
       </c>
       <c r="E135" s="21"/>
-      <c r="F135" s="30"/>
+      <c r="F135" s="51"/>
       <c r="G135" s="21"/>
     </row>
     <row r="136" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3817,7 +3817,7 @@
         <v>1000</v>
       </c>
       <c r="E136" s="21"/>
-      <c r="F136" s="30"/>
+      <c r="F136" s="51"/>
       <c r="G136" s="21"/>
     </row>
     <row r="137" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3834,7 +3834,7 @@
         <v>500</v>
       </c>
       <c r="E137" s="21"/>
-      <c r="F137" s="30"/>
+      <c r="F137" s="51"/>
       <c r="G137" s="21"/>
     </row>
     <row r="138" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3851,7 +3851,7 @@
         <v>5</v>
       </c>
       <c r="E138" s="21"/>
-      <c r="F138" s="30"/>
+      <c r="F138" s="51"/>
       <c r="G138" s="21"/>
     </row>
     <row r="139" spans="1:7" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
@@ -3868,7 +3868,7 @@
         <v>500</v>
       </c>
       <c r="E139" s="21"/>
-      <c r="F139" s="30"/>
+      <c r="F139" s="51"/>
       <c r="G139" s="21"/>
     </row>
     <row r="140" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3885,7 +3885,7 @@
         <v>3000</v>
       </c>
       <c r="E140" s="21"/>
-      <c r="F140" s="30"/>
+      <c r="F140" s="51"/>
       <c r="G140" s="21"/>
     </row>
     <row r="141" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3902,7 +3902,7 @@
         <v>1500</v>
       </c>
       <c r="E141" s="21"/>
-      <c r="F141" s="30"/>
+      <c r="F141" s="51"/>
       <c r="G141" s="21"/>
     </row>
     <row r="142" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3919,7 +3919,7 @@
         <v>2000</v>
       </c>
       <c r="E142" s="21"/>
-      <c r="F142" s="30"/>
+      <c r="F142" s="51"/>
       <c r="G142" s="21"/>
     </row>
     <row r="143" spans="1:7" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
@@ -3936,7 +3936,7 @@
         <v>1447</v>
       </c>
       <c r="E143" s="21"/>
-      <c r="F143" s="30"/>
+      <c r="F143" s="51"/>
       <c r="G143" s="21" t="s">
         <v>202</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>500</v>
       </c>
       <c r="E144" s="21"/>
-      <c r="F144" s="30"/>
+      <c r="F144" s="51"/>
       <c r="G144" s="21" t="s">
         <v>202</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>500</v>
       </c>
       <c r="E145" s="21"/>
-      <c r="F145" s="30"/>
+      <c r="F145" s="51"/>
       <c r="G145" s="21" t="s">
         <v>202</v>
       </c>
@@ -3993,7 +3993,7 @@
         <v>500</v>
       </c>
       <c r="E146" s="21"/>
-      <c r="F146" s="30"/>
+      <c r="F146" s="51"/>
       <c r="G146" s="21" t="s">
         <v>202</v>
       </c>
@@ -4012,7 +4012,7 @@
         <v>2955</v>
       </c>
       <c r="E147" s="21"/>
-      <c r="F147" s="30"/>
+      <c r="F147" s="51"/>
       <c r="G147" s="21" t="s">
         <v>202</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>1000</v>
       </c>
       <c r="E148" s="21"/>
-      <c r="F148" s="30"/>
+      <c r="F148" s="51"/>
       <c r="G148" s="21" t="s">
         <v>202</v>
       </c>
@@ -4052,7 +4052,7 @@
       <c r="E149" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="F149" s="30"/>
+      <c r="F149" s="51"/>
       <c r="G149" s="21" t="s">
         <v>202</v>
       </c>
@@ -4073,7 +4073,7 @@
       <c r="E150" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="F150" s="30"/>
+      <c r="F150" s="51"/>
       <c r="G150" s="21" t="s">
         <v>202</v>
       </c>
@@ -4094,7 +4094,7 @@
       <c r="E151" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="F151" s="30"/>
+      <c r="F151" s="51"/>
       <c r="G151" s="21" t="s">
         <v>202</v>
       </c>
@@ -4115,7 +4115,7 @@
       <c r="E152" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="F152" s="30" t="s">
+      <c r="F152" s="51" t="s">
         <v>205</v>
       </c>
       <c r="G152" s="21" t="s">
@@ -4138,7 +4138,7 @@
       <c r="E153" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="F153" s="30"/>
+      <c r="F153" s="51"/>
       <c r="G153" s="21" t="s">
         <v>202</v>
       </c>
@@ -4159,7 +4159,7 @@
       <c r="E154" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="F154" s="30"/>
+      <c r="F154" s="51"/>
       <c r="G154" s="21" t="s">
         <v>202</v>
       </c>
@@ -4180,7 +4180,7 @@
       <c r="E155" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="F155" s="30"/>
+      <c r="F155" s="51"/>
       <c r="G155" s="21" t="s">
         <v>202</v>
       </c>
@@ -4201,7 +4201,7 @@
       <c r="E156" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="F156" s="30"/>
+      <c r="F156" s="51"/>
       <c r="G156" s="21" t="s">
         <v>202</v>
       </c>
@@ -4222,7 +4222,7 @@
       <c r="E157" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="F157" s="30"/>
+      <c r="F157" s="51"/>
       <c r="G157" s="21" t="s">
         <v>202</v>
       </c>
@@ -4243,7 +4243,7 @@
       <c r="E158" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="F158" s="30"/>
+      <c r="F158" s="51"/>
       <c r="G158" s="21" t="s">
         <v>202</v>
       </c>
@@ -4264,7 +4264,7 @@
       <c r="E159" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="F159" s="30"/>
+      <c r="F159" s="51"/>
       <c r="G159" s="21" t="s">
         <v>202</v>
       </c>
@@ -4285,7 +4285,7 @@
       <c r="E160" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="F160" s="30"/>
+      <c r="F160" s="51"/>
       <c r="G160" s="21" t="s">
         <v>202</v>
       </c>
@@ -4306,7 +4306,7 @@
       <c r="E161" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="F161" s="30"/>
+      <c r="F161" s="51"/>
       <c r="G161" s="21" t="s">
         <v>202</v>
       </c>
@@ -4327,7 +4327,7 @@
       <c r="E162" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="F162" s="30"/>
+      <c r="F162" s="51"/>
       <c r="G162" s="21" t="s">
         <v>202</v>
       </c>
@@ -4348,7 +4348,7 @@
       <c r="E163" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="F163" s="30"/>
+      <c r="F163" s="51"/>
       <c r="G163" s="21" t="s">
         <v>202</v>
       </c>
@@ -4369,7 +4369,7 @@
       <c r="E164" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="F164" s="30"/>
+      <c r="F164" s="51"/>
       <c r="G164" s="21" t="s">
         <v>202</v>
       </c>
@@ -4390,7 +4390,7 @@
       <c r="E165" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="F165" s="30"/>
+      <c r="F165" s="51"/>
       <c r="G165" s="21" t="s">
         <v>202</v>
       </c>
@@ -4411,7 +4411,7 @@
       <c r="E166" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="F166" s="30" t="s">
+      <c r="F166" s="51" t="s">
         <v>205</v>
       </c>
       <c r="G166" s="21" t="s">
@@ -4434,7 +4434,7 @@
       <c r="E167" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="F167" s="30"/>
+      <c r="F167" s="51"/>
       <c r="G167" s="21" t="s">
         <v>202</v>
       </c>
@@ -4455,7 +4455,7 @@
       <c r="E168" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="F168" s="30"/>
+      <c r="F168" s="51"/>
       <c r="G168" s="21" t="s">
         <v>202</v>
       </c>
@@ -4476,7 +4476,7 @@
       <c r="E169" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="F169" s="30"/>
+      <c r="F169" s="51"/>
       <c r="G169" s="21" t="s">
         <v>202</v>
       </c>
@@ -4497,7 +4497,7 @@
       <c r="E170" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="F170" s="30"/>
+      <c r="F170" s="51"/>
       <c r="G170" s="21" t="s">
         <v>202</v>
       </c>
@@ -4518,7 +4518,7 @@
       <c r="E171" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="F171" s="30"/>
+      <c r="F171" s="51"/>
       <c r="G171" s="21" t="s">
         <v>202</v>
       </c>
@@ -4539,7 +4539,7 @@
       <c r="E172" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="F172" s="30"/>
+      <c r="F172" s="51"/>
       <c r="G172" s="21" t="s">
         <v>202</v>
       </c>
@@ -4560,7 +4560,7 @@
       <c r="E173" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="F173" s="30"/>
+      <c r="F173" s="51"/>
       <c r="G173" s="21" t="s">
         <v>202</v>
       </c>
@@ -4581,7 +4581,7 @@
       <c r="E174" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="F174" s="30"/>
+      <c r="F174" s="51"/>
       <c r="G174" s="21" t="s">
         <v>202</v>
       </c>
@@ -4602,7 +4602,7 @@
       <c r="E175" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="F175" s="30"/>
+      <c r="F175" s="51"/>
       <c r="G175" s="21" t="s">
         <v>202</v>
       </c>
@@ -4623,7 +4623,7 @@
       <c r="E176" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="F176" s="30" t="s">
+      <c r="F176" s="51" t="s">
         <v>205</v>
       </c>
       <c r="G176" s="21" t="s">
@@ -4646,7 +4646,7 @@
       <c r="E177" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="F177" s="30"/>
+      <c r="F177" s="51"/>
       <c r="G177" s="21" t="s">
         <v>203</v>
       </c>
@@ -4670,38 +4670,38 @@
       <c r="G179" s="3"/>
     </row>
     <row r="180" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="31" t="s">
+      <c r="A180" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B180" s="31"/>
-      <c r="C180" s="31" t="s">
+      <c r="B180" s="30"/>
+      <c r="C180" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D180" s="31"/>
+      <c r="D180" s="30"/>
       <c r="E180" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F180" s="31" t="s">
+      <c r="F180" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="G180" s="31"/>
+      <c r="G180" s="30"/>
     </row>
     <row r="181" spans="1:7" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="32" t="s">
+      <c r="A181" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B181" s="32"/>
-      <c r="C181" s="32" t="s">
+      <c r="B181" s="31"/>
+      <c r="C181" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D181" s="32"/>
+      <c r="D181" s="31"/>
       <c r="E181" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="F181" s="32" t="s">
+      <c r="F181" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="G181" s="32"/>
+      <c r="G181" s="31"/>
     </row>
     <row r="182" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A182" s="13"/>
@@ -4749,21 +4749,21 @@
       <c r="G186" s="13"/>
     </row>
     <row r="187" spans="1:7" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="31" t="s">
+      <c r="A187" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B187" s="31"/>
-      <c r="C187" s="31" t="s">
+      <c r="B187" s="30"/>
+      <c r="C187" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="D187" s="31"/>
+      <c r="D187" s="30"/>
       <c r="E187" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F187" s="31" t="s">
+      <c r="F187" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="G187" s="31"/>
+      <c r="G187" s="30"/>
     </row>
     <row r="188" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="189" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4787,18 +4787,8 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A180:B180"/>
-    <mergeCell ref="A181:B181"/>
-    <mergeCell ref="A187:B187"/>
-    <mergeCell ref="C180:D180"/>
-    <mergeCell ref="C181:D181"/>
-    <mergeCell ref="C187:D187"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="F10:F55"/>
+    <mergeCell ref="F56:F107"/>
     <mergeCell ref="F176:F177"/>
     <mergeCell ref="F180:G180"/>
     <mergeCell ref="F181:G181"/>
@@ -4806,8 +4796,18 @@
     <mergeCell ref="F108:F151"/>
     <mergeCell ref="F152:F165"/>
     <mergeCell ref="F166:F175"/>
-    <mergeCell ref="F10:F55"/>
-    <mergeCell ref="F56:F107"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="A180:B180"/>
+    <mergeCell ref="A181:B181"/>
+    <mergeCell ref="A187:B187"/>
+    <mergeCell ref="C180:D180"/>
+    <mergeCell ref="C181:D181"/>
+    <mergeCell ref="C187:D187"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
